--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939C1087-C8DC-4241-8B1A-AF4E8F83936C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4641E27-3657-4227-B961-E537F62CE4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,10 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>위치 무관</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>가운데 4X4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -124,6 +120,14 @@
   </si>
   <si>
     <t>10X10, 9X9 라인 2줄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총알 수(타워만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공장, 혹은 다른 도로의 상하좌우 위치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -450,18 +454,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="30.25" customWidth="1"/>
+    <col min="4" max="4" width="34.125" customWidth="1"/>
     <col min="5" max="5" width="19.75" customWidth="1"/>
     <col min="6" max="6" width="27.75" customWidth="1"/>
     <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -489,18 +494,18 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -511,7 +516,7 @@
         <v>200</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -520,12 +525,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -536,7 +541,7 @@
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -545,12 +550,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -561,7 +566,7 @@
         <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -570,15 +575,18 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -589,7 +597,7 @@
         <v>150</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -600,8 +608,11 @@
       <c r="G14">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -612,7 +623,7 @@
         <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -622,6 +633,9 @@
       </c>
       <c r="G15">
         <v>35</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4641E27-3657-4227-B961-E537F62CE4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9667C753-7D7B-4E8B-B1A2-E564AE8767EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -522,7 +522,7 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9667C753-7D7B-4E8B-B1A2-E564AE8767EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840890C5-FA9B-4972-B42E-D6EC5F53E5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -522,7 +522,7 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840890C5-FA9B-4972-B42E-D6EC5F53E5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61B260C-749B-4A7C-B115-32AA4BFFB60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cannon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>총알 생산 증가량(공장 버프만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>타워 공격력 증가량(타워 버프만)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,6 +120,70 @@
   </si>
   <si>
     <t>공장, 혹은 다른 도로의 상하좌우 위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slingshot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 총알 타입(타워만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총알</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4X4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StoneFactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArrowFactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AmmoFactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요재료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산 증가량(공장 버프만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쇠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동그란 돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살, 동그란 돌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -454,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -464,9 +520,10 @@
     <col min="6" max="6" width="27.75" customWidth="1"/>
     <col min="7" max="7" width="17.5" customWidth="1"/>
     <col min="8" max="8" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,16 +531,16 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -494,148 +551,250 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>200</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="C7">
+      <c r="C9">
         <v>100</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>150</v>
+      </c>
+      <c r="D16" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>0.7</v>
+      </c>
+      <c r="G16">
+        <v>50</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>200</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>1.2</v>
+      </c>
+      <c r="G17">
+        <v>35</v>
+      </c>
+      <c r="H17">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10">
-        <v>200</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>150</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14">
-        <v>0.7</v>
-      </c>
-      <c r="G14">
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18">
+        <v>300</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
         <v>50</v>
       </c>
-      <c r="H14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15">
-        <v>200</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="H18">
         <v>10</v>
       </c>
-      <c r="F15">
-        <v>1.2</v>
-      </c>
-      <c r="G15">
-        <v>35</v>
-      </c>
-      <c r="H15">
-        <v>5</v>
+      <c r="I18" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61B260C-749B-4A7C-B115-32AA4BFFB60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FEE7E2-39F8-4BEB-BAB0-7E6923AEE04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,14 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3X3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2X2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>공격속도(타워만)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,10 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4X4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>StoneFactory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -184,6 +172,10 @@
   </si>
   <si>
     <t>화살, 동그란 돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 범위(타워만)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,10 +526,10 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -551,21 +543,21 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -573,25 +565,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -599,25 +591,25 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>150</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -625,30 +617,30 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -662,10 +654,10 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -673,7 +665,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -687,27 +679,30 @@
         <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1">
         <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -715,16 +710,16 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
       </c>
       <c r="F16">
         <v>0.7</v>
@@ -736,7 +731,7 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -750,10 +745,10 @@
         <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
       </c>
       <c r="F17">
         <v>1.2</v>
@@ -765,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -773,16 +768,16 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
+        <v>19</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -794,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="I18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FEE7E2-39F8-4BEB-BAB0-7E6923AEE04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9BCC78-C489-4B37-BF2A-543D8667AEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>초당 총알 생산(공장만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>효과 범위</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -107,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>총알 수(타워만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>공장, 혹은 다른 도로의 상하좌우 위치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,6 +168,18 @@
   </si>
   <si>
     <t>공격 범위(타워만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 재료 생산(공장만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요재료 최대 수용량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과물 최대 보유량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -502,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -510,12 +514,12 @@
     <col min="4" max="4" width="34.125" customWidth="1"/>
     <col min="5" max="5" width="19.75" customWidth="1"/>
     <col min="6" max="6" width="27.75" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="15.375" customWidth="1"/>
-    <col min="9" max="9" width="29.875" customWidth="1"/>
+    <col min="7" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="15.375" customWidth="1"/>
+    <col min="10" max="10" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,13 +530,13 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -543,35 +547,41 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -580,24 +590,30 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>150</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -606,24 +622,30 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -632,18 +654,24 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -654,7 +682,7 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -663,12 +691,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -679,7 +707,7 @@
         <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -688,9 +716,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -699,24 +727,24 @@
         <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -731,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -745,7 +773,7 @@
         <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -760,7 +788,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -768,13 +796,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>15</v>
@@ -789,7 +817,7 @@
         <v>10</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9BCC78-C489-4B37-BF2A-543D8667AEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F694F-E4DE-4265-820B-62E902BF1491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,30 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소환 가능 범위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가운데 4X4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가운데 5X5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10X10, 9X9, 8X8 라인 3줄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10X10, 9X9 라인 2줄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공장, 혹은 다른 도로의 상하좌우 위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Slingshot</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,6 +156,18 @@
   </si>
   <si>
     <t>결과물 최대 보유량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소환 가능 구역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마을</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타워 구역</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -530,7 +518,7 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
         <v>13</v>
@@ -547,7 +535,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -555,19 +543,19 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -575,13 +563,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -590,13 +578,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -607,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>150</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -622,13 +610,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -639,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -654,13 +642,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -668,7 +656,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -682,7 +670,7 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -707,7 +695,7 @@
         <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -718,7 +706,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -727,10 +715,10 @@
         <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -738,13 +726,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -759,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -773,7 +761,7 @@
         <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -788,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -796,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>15</v>
@@ -817,7 +805,7 @@
         <v>10</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F694F-E4DE-4265-820B-62E902BF1491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99659CDA-312C-4342-B397-1B05A13D0285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격속도(타워만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>공격력(타워만)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,6 +164,10 @@
   </si>
   <si>
     <t>타워 구역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도-초당 공격수(타워만)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -518,10 +518,10 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -535,27 +535,27 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
         <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -563,28 +563,28 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -595,28 +595,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>150</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -627,28 +627,28 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -656,7 +656,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -670,10 +670,10 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -695,10 +695,10 @@
         <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1">
         <v>0.5</v>
@@ -706,19 +706,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
         <v>9</v>
       </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -726,13 +726,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -776,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -784,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>15</v>
@@ -805,7 +805,7 @@
         <v>10</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99659CDA-312C-4342-B397-1B05A13D0285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B531913-9C51-431F-86A6-B70977FBE166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -630,7 +630,7 @@
         <v>21</v>
       </c>
       <c r="C6">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -787,7 +787,7 @@
         <v>18</v>
       </c>
       <c r="C18">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B531913-9C51-431F-86A6-B70977FBE166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DF01BD-FDE2-48E9-A776-CF8376CA329D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,6 +168,38 @@
   </si>
   <si>
     <t>공격속도-초당 공격수(타워만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 간 재료들의 연결 범위를 늘려줌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌을 동그란돌로 만드는 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쇠를 화살로 만드는 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살, 동그란 돌을 총알로 만드는 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동그란 돌을 사용하는 타워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총알 사용하는 타워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살 사용하는 타워</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -505,9 +537,10 @@
     <col min="7" max="8" width="17.5" customWidth="1"/>
     <col min="9" max="9" width="15.375" customWidth="1"/>
     <col min="10" max="10" width="29.875" customWidth="1"/>
+    <col min="11" max="11" width="90.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,8 +556,11 @@
       <c r="E1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -540,8 +576,11 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
         <v>29</v>
       </c>
@@ -558,7 +597,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -589,8 +628,11 @@
       <c r="J4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -621,8 +663,11 @@
       <c r="J5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -653,13 +698,16 @@
       <c r="J6">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -679,12 +727,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -704,7 +752,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
         <v>28</v>
       </c>
@@ -721,7 +769,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -749,8 +797,11 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -778,8 +829,11 @@
       <c r="I17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -806,6 +860,9 @@
       </c>
       <c r="I18" t="s">
         <v>17</v>
+      </c>
+      <c r="K18" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
